--- a/output/pdf_financials_xlsx/DEC.xlsx
+++ b/output/pdf_financials_xlsx/DEC.xlsx
@@ -1085,10 +1085,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000452</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>1.2e-05</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -2104,10 +2104,10 @@
         <v>-0.740552</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.355268</v>
+        <v>-2.35572</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.7456469999999999</v>
+        <v>-0.745659</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-2.063472</v>
@@ -2234,10 +2234,10 @@
         <v>-0.71391</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.301369</v>
+        <v>-2.301821</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.686991</v>
+        <v>-0.687003</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-2.018348</v>
@@ -2539,52 +2539,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.429798</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.905565</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.485779</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.008049000000000001</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.000565</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.019747</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000192</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.002156</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.093835</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.075638</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.147832</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.275014</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.245891</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.795909</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.02556</v>
       </c>
     </row>
     <row r="35">
@@ -2649,52 +2649,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.429798</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.905565</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.485779</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.008049000000000001</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.000565</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.019747</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000192</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.002156</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.093835</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.075638</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.147832</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.275014</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.245891</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.795909</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.03</v>
+        <v>0.05556</v>
       </c>
     </row>
     <row r="37">
@@ -3309,52 +3309,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.471042</v>
+        <v>0.041244</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.087489</v>
+        <v>0.181924</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.845644</v>
+        <v>0.359865</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.013518</v>
+        <v>0.005469</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.007919000000000001</v>
+        <v>0.007354</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.069323</v>
+        <v>0.049576</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.003848</v>
+        <v>0.003656</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.09378499999999999</v>
+        <v>0.091629</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.501983</v>
+        <v>0.408148</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.001138</v>
+        <v>0.9255</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.170715</v>
+        <v>0.022883</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.307175</v>
+        <v>0.032161</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.036683</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.283939</v>
+        <v>0.038048</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.89774</v>
+        <v>0.101831</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.04206</v>
+        <v>0.0165</v>
       </c>
     </row>
     <row r="49">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -8930,7 +8930,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>0.008262</v>
       </c>
@@ -16622,7 +16626,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
@@ -17100,7 +17104,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E99" s="5" t="n">
         <v>0.008262</v>
       </c>
@@ -19248,7 +19256,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -27882,7 +27894,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E216" s="5" t="n">
         <v>-0.002262</v>
       </c>
@@ -34696,7 +34712,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">

--- a/output/pdf_financials_xlsx/DEC.xlsx
+++ b/output/pdf_financials_xlsx/DEC.xlsx
@@ -754,37 +754,37 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.258847</v>
+        <v>0.424347</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.312529</v>
+        <v>0.522529</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.196601</v>
+        <v>0.350601</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.264801</v>
+        <v>0.389401</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.153944</v>
+        <v>0.219944</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.131822</v>
+        <v>0.233322</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.074645</v>
+        <v>0.158645</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.11365</v>
+        <v>0.200332</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.194865</v>
+        <v>0.543753</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.143345</v>
+        <v>0.762225</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.146536</v>
+        <v>0.494536</v>
       </c>
       <c r="M7" s="1" t="inlineStr">
         <is>
@@ -949,37 +949,37 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.258847</v>
+        <v>0.424347</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.351556</v>
+        <v>0.5615560000000001</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.233775</v>
+        <v>0.387775</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.284287</v>
+        <v>0.408887</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.157446</v>
+        <v>0.223446</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.135105</v>
+        <v>0.236605</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.074645</v>
+        <v>0.158645</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.11365</v>
+        <v>0.200332</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.201515</v>
+        <v>0.550403</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.143345</v>
+        <v>0.762225</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.146536</v>
+        <v>0.494536</v>
       </c>
       <c r="M10" s="1" t="inlineStr">
         <is>
@@ -1014,37 +1014,37 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.258847</v>
+        <v>-0.424347</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.351556</v>
+        <v>-0.5615560000000001</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.233775</v>
+        <v>-0.387775</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.284287</v>
+        <v>-0.408887</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.157446</v>
+        <v>-0.223446</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.135105</v>
+        <v>-0.236605</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.074645</v>
+        <v>-0.158645</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.11365</v>
+        <v>-0.200332</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.201515</v>
+        <v>-0.550403</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.143345</v>
+        <v>-0.762225</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.146536</v>
+        <v>-0.494536</v>
       </c>
       <c r="M11" s="1" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0</v>
+        <v>0.613116</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -1289,22 +1289,22 @@
         <v>0.038925</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0</v>
+        <v>0.199653</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0</v>
+        <v>0.04245</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0</v>
+        <v>0.010476</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
+        <v>0.099012</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0</v>
+        <v>1e-05</v>
       </c>
       <c r="M15" s="1" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>0.11264</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>0.352764</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>0</v>
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>0</v>
+        <v>-0.055331</v>
       </c>
     </row>
     <row r="38">
@@ -2927,10 +2927,10 @@
         <v>0.055774</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.424025</v>
+        <v>0.5366649999999999</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.051813</v>
+        <v>0.404577</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>0.026191</v>
@@ -2969,7 +2969,7 @@
         <v>0.071822</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>0.03375</v>
+        <v>-0.021581</v>
       </c>
     </row>
     <row r="42">
@@ -3312,10 +3312,10 @@
         <v>0.041244</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.181924</v>
+        <v>0.069284</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.359865</v>
+        <v>0.007101</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.005469</v>
@@ -3354,7 +3354,7 @@
         <v>0.101831</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.0165</v>
+        <v>0.07183100000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3891,52 +3891,52 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>0</v>
+        <v>0.08873499999999999</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>0</v>
+        <v>0.32521</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>0</v>
+        <v>0.371088</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0</v>
+        <v>0.468534</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0</v>
+        <v>0.288564</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0</v>
+        <v>0.254433</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0</v>
+        <v>0.210302</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0</v>
+        <v>0.191498</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0</v>
+        <v>0.018895</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0</v>
+        <v>0.015061</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0</v>
+        <v>-0.8346710000000001</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>0</v>
+        <v>-0.288207</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>0</v>
+        <v>0.004357</v>
       </c>
       <c r="O58" s="3" t="n">
-        <v>-0.635845</v>
+        <v>-0.632372</v>
       </c>
       <c r="P58" s="3" t="n">
-        <v>0</v>
+        <v>-0.367631</v>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>0</v>
+        <v>-8.768331999999999</v>
       </c>
     </row>
     <row r="59">
@@ -4056,52 +4056,52 @@
         </is>
       </c>
       <c r="B61" s="3" t="n">
-        <v>1.674199</v>
+        <v>1.585464</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>2.845234</v>
+        <v>2.520024</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>9.929157999999999</v>
+        <v>9.558070000000001</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>11.491837</v>
+        <v>11.023303</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>11.397615</v>
+        <v>11.109051</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>12.31172</v>
+        <v>12.057287</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>9.850225999999999</v>
+        <v>9.639924000000001</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>10.304387</v>
+        <v>10.112889</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>12.394011</v>
+        <v>12.375116</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>11.845039</v>
+        <v>11.829978</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>10.809486</v>
+        <v>11.644157</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>12.525087</v>
+        <v>12.813294</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>14.153107</v>
+        <v>14.14875</v>
       </c>
       <c r="O61" s="3" t="n">
-        <v>14.86453</v>
+        <v>14.861057</v>
       </c>
       <c r="P61" s="3" t="n">
-        <v>16.321881</v>
+        <v>16.689512</v>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>10.079026</v>
+        <v>18.847358</v>
       </c>
     </row>
     <row r="62">
@@ -4361,7 +4361,7 @@
         <v>0</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0</v>
+        <v>0.2195</v>
       </c>
       <c r="M66" s="3" t="n">
         <v>0</v>
@@ -4450,10 +4450,10 @@
         <v>0.281373</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>0.452851</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>0.911417</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>1.099193</v>
@@ -5605,52 +5605,52 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>3.999232</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>10.976374</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>12.637307</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>13.916407</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>15.481127</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>16.451611</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>16.451611</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>17.728798</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>21.286057</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0</v>
+        <v>23.38135</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0</v>
+        <v>23.40535</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>0</v>
+        <v>26.51466</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>0</v>
+        <v>28.210928</v>
       </c>
       <c r="O88" s="3" t="n">
-        <v>0</v>
+        <v>29.468227</v>
       </c>
       <c r="P88" s="3" t="n">
-        <v>0</v>
+        <v>32.198722</v>
       </c>
       <c r="Q88" s="3" t="n">
-        <v>0</v>
+        <v>34.203194</v>
       </c>
     </row>
     <row r="89">
@@ -8772,7 +8772,11 @@
           <t>Prepaid expenses – Note 7</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>-</t>
@@ -9000,7 +9004,11 @@
           <t>Property and equipment – Note 4</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -9624,7 +9632,11 @@
           <t>Share capital – Note 6</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11074,7 +11086,11 @@
           <t>Write-off of exploration and evaluation assets – Note 5</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -11162,7 +11178,11 @@
           <t>Write-off of accounts receivable – Note 5</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -12716,7 +12736,11 @@
           <t>Due to related parties – Note 7</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>OtherPayable</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -13098,7 +13122,11 @@
           <t>Loss on sale of property and equipment – Note 7</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -13458,7 +13486,11 @@
           <t>Share capital – Note 6</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -14454,7 +14486,11 @@
           <t>Property and equipment – Notes 4 and 7</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -14548,7 +14584,11 @@
           <t>Accounts payable and accrued liabilities – Notes 5 and 7 $</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -14642,7 +14682,11 @@
           <t>Accounts receivable – Notes 6 and 8</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -14738,7 +14782,11 @@
           <t>Prepaid expenses – Note 8</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -14926,7 +14974,11 @@
           <t>Property and equipment – Notes 5 and 8</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -15114,7 +15166,11 @@
           <t>Accounts payable and accrued liabilities – Notes 6 and 8 $</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -15306,7 +15362,11 @@
           <t>Share capital – Note 7</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E80" s="5" t="n">
         <v>3.078359</v>
       </c>
@@ -15396,7 +15456,11 @@
           <t>Accounts receivable – Notes 6 and 9</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -15678,7 +15742,11 @@
           <t>Property and equipment – Notes 5 and 9</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="n">
         <v>0.08873499999999999</v>
       </c>
@@ -15770,7 +15838,11 @@
           <t>Mineral properties – Notes 6 and 9</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>MineralProperties</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
         <v>2.857862</v>
       </c>
@@ -16340,7 +16412,11 @@
           <t>Share capital – Note 8</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E91" s="5" t="n">
         <v>3.999232</v>
       </c>
@@ -16820,7 +16896,11 @@
           <t>Accounts receivable – Notes 5 and 8</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AccountsReceivable</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -17202,7 +17282,11 @@
           <t>Property and equipment – Notes 4 and 8</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
         <v>0.08873499999999999</v>
       </c>
@@ -17772,7 +17856,11 @@
           <t>Contributed surplus – Note 7</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E106" s="5" t="n">
         <v>0.882033</v>
       </c>
@@ -30008,7 +30096,11 @@
           <t>Consulting fees – Note 7</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -30416,7 +30508,11 @@
           <t>Management fees – Note 7</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -30996,7 +31092,11 @@
           <t>Other income – Notes 6 and 7</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -32562,7 +32662,11 @@
           <t>Other income – Note 7</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -32750,7 +32854,11 @@
           <t>Deferred income tax expense – Note 11</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -33024,7 +33132,11 @@
           <t>Depreciation – Note 4</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -33114,7 +33226,11 @@
           <t>Other income – Note 6</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E273" t="inlineStr">
         <is>
           <t>-</t>
@@ -34338,7 +34454,11 @@
           <t>Management fees – Note 8</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E286" s="5" t="n">
         <v>0.1425</v>
       </c>
@@ -34522,7 +34642,11 @@
           <t>Rent – Note 8</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E288" s="5" t="n">
         <v>0.023</v>
       </c>
@@ -35000,7 +35124,11 @@
           <t>Deferred income taxes – Note 12</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -35188,7 +35316,11 @@
           <t>Management fees – Note 9</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -35376,7 +35508,11 @@
           <t>Rent – Note 9</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -35660,7 +35796,11 @@
           <t>Other income – Note 14</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -35756,7 +35896,11 @@
           <t>Deferred income taxes – Note 13</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DEC.xlsx
+++ b/output/pdf_financials_xlsx/DEC.xlsx
@@ -6889,25 +6889,25 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.175</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.058001</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>0.175799</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -20566,7 +20566,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/DEC.xlsx
+++ b/output/pdf_financials_xlsx/DEC.xlsx
@@ -1416,7 +1416,7 @@
         <v>0.569178</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.340281</v>
+        <v>-0.42</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>0.595437</v>
@@ -2392,7 +2392,7 @@
         <v>-76.33343928159036</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-16.49070110958617</v>
+        <v>-20.35404405778222</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-124.8528551448803</v>
@@ -6296,28 +6296,28 @@
         <v>0</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>-0.319486</v>
+        <v>-0.309527</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002298</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>-7.3e-05</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>-0.043995</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>0.030977</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>-0.033276</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>-0.016633</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0.045331</v>
+        <v>0.08340400000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6571,28 +6571,28 @@
         <v>0.053611</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.31572</v>
+        <v>-0.305761</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.067713</v>
+        <v>0.065415</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.028649</v>
+        <v>0.028576</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.003969</v>
+        <v>-0.047964</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.044904</v>
+        <v>0.075881</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>-0.025083</v>
+        <v>-0.058359</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>-0.077801</v>
+        <v>-0.094434</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.169015</v>
+        <v>0.207088</v>
       </c>
     </row>
     <row r="107">
@@ -18042,7 +18042,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -18710,7 +18714,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -19098,7 +19106,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -20758,7 +20770,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -26466,7 +26482,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -31548,7 +31568,11 @@
           <t>Deferred income tax recovery – Note 11</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -32294,7 +32318,11 @@
           <t>Deferred income tax recovery (expense) – Note 11</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -33608,7 +33636,11 @@
           <t>Deferred income tax recovery (expense) – Note 11</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -34180,7 +34212,11 @@
           <t>Deferred income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
